--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Page Title</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
